--- a/public/downloads/ZhengOrigin2020.xlsx
+++ b/public/downloads/ZhengOrigin2020.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>HO2</t>
   </si>
   <si>
-    <t>O</t>
+    <t>HO</t>
   </si>
   <si>
-    <t>HO</t>
+    <t>O</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>16</v>
       </c>
       <c r="N3" s="5">
-        <v>2480.98989033699</v>
+        <v>2480989.89033699</v>
       </c>
       <c r="O3" s="4">
-        <v>0.387957762367004</v>
+        <v>387.957762367004</v>
       </c>
       <c r="P3" s="5">
         <v>6395</v>
@@ -709,10 +732,10 @@
         <v>16</v>
       </c>
       <c r="N4" s="5">
-        <v>1425.89009976387</v>
+        <v>1425890.09976387</v>
       </c>
       <c r="O4" s="4">
-        <v>0.2080983800005648</v>
+        <v>208.0983800005648</v>
       </c>
       <c r="P4" s="5">
         <v>6852</v>
@@ -759,10 +782,10 @@
         <v>16</v>
       </c>
       <c r="N5" s="5">
-        <v>1210.530505418777</v>
+        <v>1210530.505418777</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1911162780894818</v>
+        <v>191.1162780894818</v>
       </c>
       <c r="P5" s="5">
         <v>6334</v>
@@ -809,10 +832,10 @@
         <v>16</v>
       </c>
       <c r="N6" s="5">
-        <v>1065.435245037079</v>
+        <v>1065435.245037079</v>
       </c>
       <c r="O6" s="4">
-        <v>0.141360653447934</v>
+        <v>141.360653447934</v>
       </c>
       <c r="P6" s="5">
         <v>7537</v>
@@ -859,10 +882,10 @@
         <v>16</v>
       </c>
       <c r="N7" s="5">
-        <v>1604.838933229446</v>
+        <v>1604838.933229446</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2368066892768845</v>
+        <v>236.8066892768845</v>
       </c>
       <c r="P7" s="5">
         <v>6777</v>
@@ -909,10 +932,10 @@
         <v>16</v>
       </c>
       <c r="N8" s="5">
-        <v>537.7253928184509</v>
+        <v>537725.3928184509</v>
       </c>
       <c r="O8" s="4">
-        <v>0.08633997957907048</v>
+        <v>86.33997957907049</v>
       </c>
       <c r="P8" s="5">
         <v>6228</v>
@@ -959,10 +982,10 @@
         <v>16</v>
       </c>
       <c r="N9" s="5">
-        <v>468.6295921802521</v>
+        <v>468629.5921802521</v>
       </c>
       <c r="O9" s="4">
-        <v>0.09465352296106889</v>
+        <v>94.6535229610689</v>
       </c>
       <c r="P9" s="5">
         <v>4951</v>
@@ -1009,10 +1032,10 @@
         <v>16</v>
       </c>
       <c r="N10" s="5">
-        <v>581.9544486999512</v>
+        <v>581954.4486999512</v>
       </c>
       <c r="O10" s="4">
-        <v>0.0878024213488158</v>
+        <v>87.8024213488158</v>
       </c>
       <c r="P10" s="5">
         <v>6628</v>
@@ -1059,10 +1082,10 @@
         <v>16</v>
       </c>
       <c r="N11" s="5">
-        <v>663.0069465637207</v>
+        <v>663006.9465637207</v>
       </c>
       <c r="O11" s="4">
-        <v>0.09673284892963535</v>
+        <v>96.73284892963535</v>
       </c>
       <c r="P11" s="5">
         <v>6854</v>
@@ -1109,10 +1132,10 @@
         <v>16</v>
       </c>
       <c r="N12" s="5">
-        <v>472.8456017971039</v>
+        <v>472845.6017971039</v>
       </c>
       <c r="O12" s="4">
-        <v>0.07867647284477602</v>
+        <v>78.67647284477603</v>
       </c>
       <c r="P12" s="5">
         <v>6010</v>
@@ -1159,10 +1182,10 @@
         <v>16</v>
       </c>
       <c r="N13" s="5">
-        <v>630.3168060779572</v>
+        <v>630316.8060779572</v>
       </c>
       <c r="O13" s="4">
-        <v>0.1379249028616974</v>
+        <v>137.9249028616974</v>
       </c>
       <c r="P13" s="5">
         <v>4570</v>
@@ -1209,10 +1232,10 @@
         <v>16</v>
       </c>
       <c r="N14" s="5">
-        <v>2044.4356944561</v>
+        <v>2044435.6944561</v>
       </c>
       <c r="O14" s="4">
-        <v>0.294502404848185</v>
+        <v>294.502404848185</v>
       </c>
       <c r="P14" s="5">
         <v>6942</v>
@@ -1259,10 +1282,10 @@
         <v>16</v>
       </c>
       <c r="N15" s="5">
-        <v>2151.287494659424</v>
+        <v>2151287.494659424</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2821360648733671</v>
+        <v>282.136064873367</v>
       </c>
       <c r="P15" s="5">
         <v>7625</v>
@@ -1309,10 +1332,10 @@
         <v>16</v>
       </c>
       <c r="N16" s="5">
-        <v>972.4899475574493</v>
+        <v>972489.9475574493</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1334920998706176</v>
+        <v>133.4920998706176</v>
       </c>
       <c r="P16" s="5">
         <v>7285</v>
@@ -1359,10 +1382,10 @@
         <v>16</v>
       </c>
       <c r="N17" s="5">
-        <v>844.284651517868</v>
+        <v>844284.651517868</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1129175674091037</v>
+        <v>112.9175674091037</v>
       </c>
       <c r="P17" s="5">
         <v>7477</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,34 +1497,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2287820346602215</v>
+        <v>0.5442778698846867</v>
       </c>
       <c r="C3" s="4">
-        <v>0.063245658691919</v>
+        <v>0.4560612804782605</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1934692197114559</v>
+        <v>0.5353602268401397</v>
       </c>
       <c r="E3" s="4">
-        <v>58.63945578231325</v>
+        <v>56.19047619047646</v>
       </c>
       <c r="F3" s="4">
-        <v>48.43027591349797</v>
+        <v>49.98322147651101</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>3</v>
@@ -1501,25 +1556,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5442778698846867</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4560612804782605</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2007564484634605</v>
+        <v>0.303280516163391</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1104467942804783</v>
+        <v>0.05823116950087659</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1832211893341766</v>
+        <v>0.2803853537696664</v>
       </c>
       <c r="E4" s="4">
-        <v>52.81632653061224</v>
+        <v>48.77551020408163</v>
       </c>
       <c r="F4" s="4">
-        <v>45.06711409395973</v>
+        <v>42.41610738255034</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -1542,25 +1613,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.303280516163391</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05823116950087659</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.08302315062740825</v>
+        <v>0.3823283592277328</v>
       </c>
       <c r="C5" s="4">
-        <v>0.004227972466152252</v>
+        <v>0.03695920820657239</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1343137478680298</v>
+        <v>0.3303512530008025</v>
       </c>
       <c r="E5" s="4">
-        <v>52.40816326530612</v>
+        <v>49.81632653061224</v>
       </c>
       <c r="F5" s="4">
-        <v>44.35570469798657</v>
+        <v>44.74496644295302</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -1583,9 +1670,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3823283592277328</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03695920820657239</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1699,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1718,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1760,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,25 +1791,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3276651689396128</v>
+        <v>0.8452845343086892</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4413440517407423</v>
+        <v>0.9126482299786574</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4613907596618863</v>
+        <v>0.992285515979025</v>
       </c>
       <c r="E3" s="4">
-        <v>57.3752834467123</v>
+        <v>57.65306122449013</v>
       </c>
       <c r="F3" s="4">
-        <v>49.27479492915828</v>
+        <v>54.6718866517523</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -1714,25 +1850,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8452845343086892</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.9126482299786574</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2903009755131734</v>
+        <v>0.5626728213270212</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3394574658813383</v>
+        <v>0.6315100229754478</v>
       </c>
       <c r="D4" s="4">
-        <v>0.34636825151415</v>
+        <v>0.6403410590131784</v>
       </c>
       <c r="E4" s="4">
-        <v>51.93877551020408</v>
+        <v>51.02040816326531</v>
       </c>
       <c r="F4" s="4">
-        <v>44.18568232662193</v>
+        <v>50.30201342281873</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -1755,25 +1907,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5626728213270212</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6315100229754478</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.226035012476575</v>
+        <v>0.8941001134641056</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2028346098437339</v>
+        <v>1.033865405792227</v>
       </c>
       <c r="D5" s="4">
-        <v>0.287958721829807</v>
+        <v>0.9432829099423771</v>
       </c>
       <c r="E5" s="4">
-        <v>50.85714285714285</v>
+        <v>50.83673469387755</v>
       </c>
       <c r="F5" s="4">
-        <v>43.4675615212528</v>
+        <v>50.77628635346756</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -1796,9 +1964,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8941001134641056</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.033865405792227</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +1993,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2001,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2012,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2054,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,34 +2085,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.305054254366856</v>
+        <v>0.2287820346602215</v>
       </c>
       <c r="C3" s="4">
-        <v>0.07288907630286683</v>
+        <v>0.063245658691919</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2021870739713449</v>
+        <v>0.1934692197114559</v>
       </c>
       <c r="E3" s="4">
-        <v>55.85034013605485</v>
+        <v>58.63945578231325</v>
       </c>
       <c r="F3" s="4">
-        <v>48.00708426547418</v>
+        <v>48.43027591349797</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>3</v>
@@ -1927,25 +2144,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2287820346602215</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.063245658691919</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2536291318662052</v>
+        <v>0.08302315062740825</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1190108792724516</v>
+        <v>0.004227972466152252</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1858797269589786</v>
+        <v>0.1343137478680298</v>
       </c>
       <c r="E4" s="4">
-        <v>52.14285714285715</v>
+        <v>52.40816326530612</v>
       </c>
       <c r="F4" s="4">
-        <v>49.15436241610723</v>
+        <v>44.35570469798657</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -1960,33 +2193,49 @@
         <v>3</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08302315062740825</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.004227972466152252</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2723633318276484</v>
+        <v>0.2007564484634605</v>
       </c>
       <c r="C5" s="4">
-        <v>0.0321492322265442</v>
+        <v>0.1104467942804783</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1957998878618241</v>
+        <v>0.1832211893341766</v>
       </c>
       <c r="E5" s="4">
-        <v>50.38095238095239</v>
+        <v>52.81632653061224</v>
       </c>
       <c r="F5" s="4">
-        <v>45.53914988814319</v>
+        <v>45.06711409395973</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -2001,17 +2250,33 @@
         <v>3</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2007564484634605</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1104467942804783</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2287,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2295,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2306,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2348,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,25 +2379,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1870887690364498</v>
+        <v>0.3276651689396128</v>
       </c>
       <c r="C3" s="4">
-        <v>0.03855100925781585</v>
+        <v>0.4413440517407423</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2137812659883783</v>
+        <v>0.4613907596618863</v>
       </c>
       <c r="E3" s="4">
-        <v>58.26530612244924</v>
+        <v>57.3752834467123</v>
       </c>
       <c r="F3" s="4">
-        <v>57.63795674869591</v>
+        <v>49.27479492915828</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2140,25 +2438,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3276651689396128</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4413440517407423</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3646908956296329</v>
+        <v>0.226035012476575</v>
       </c>
       <c r="C4" s="4">
-        <v>0.05433411764525431</v>
+        <v>0.2028346098437339</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2119225615231926</v>
+        <v>0.287958721829807</v>
       </c>
       <c r="E4" s="4">
-        <v>52.87755102040816</v>
+        <v>50.85714285714285</v>
       </c>
       <c r="F4" s="4">
-        <v>56.85011185682262</v>
+        <v>43.4675615212528</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -2181,25 +2495,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.226035012476575</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2028346098437339</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2868722306837412</v>
+        <v>0.2903009755131734</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1280372106060952</v>
+        <v>0.3394574658813383</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2072492138101666</v>
+        <v>0.34636825151415</v>
       </c>
       <c r="E5" s="4">
-        <v>51.79591836734694</v>
+        <v>51.93877551020408</v>
       </c>
       <c r="F5" s="4">
-        <v>51.54362416107382</v>
+        <v>44.18568232662193</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -2222,9 +2552,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2903009755131734</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3394574658813383</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2581,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2589,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2600,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2642,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,34 +2673,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5957789151007257</v>
+        <v>0.305054254366856</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3483723393899627</v>
+        <v>0.07288907630286683</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4802161781124307</v>
+        <v>0.2021870739713449</v>
       </c>
       <c r="E3" s="4">
-        <v>48.88888888888903</v>
+        <v>55.85034013605485</v>
       </c>
       <c r="F3" s="4">
-        <v>45.24422073079798</v>
+        <v>48.00708426547418</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>3</v>
@@ -2353,25 +2732,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.305054254366856</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07288907630286683</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3498992251270979</v>
+        <v>0.2723633318276484</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4444946037472439</v>
+        <v>0.0321492322265442</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4178002746766252</v>
+        <v>0.1957998878618241</v>
       </c>
       <c r="E4" s="4">
-        <v>42.30612244897959</v>
+        <v>50.38095238095239</v>
       </c>
       <c r="F4" s="4">
-        <v>37.31767337807607</v>
+        <v>45.53914988814319</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -2386,58 +2781,90 @@
         <v>3</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2723633318276484</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0321492322265442</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3963628785540602</v>
+        <v>0.2536291318662052</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>0.1190108792724516</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3320856596454412</v>
+        <v>0.1858797269589786</v>
       </c>
       <c r="E5" s="4">
-        <v>39.60544217687075</v>
+        <v>52.14285714285715</v>
       </c>
       <c r="F5" s="4">
-        <v>23.91498881431764</v>
+        <v>49.15436241610723</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2536291318662052</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1190108792724516</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2875,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2883,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2894,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2936,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2967,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6940909066645856</v>
+        <v>0.1870887690364498</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4945518382565552</v>
+        <v>0.03855100925781585</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3310876924641815</v>
+        <v>0.2137812659883783</v>
       </c>
       <c r="E3" s="4">
-        <v>57.73809523809553</v>
+        <v>58.26530612244924</v>
       </c>
       <c r="F3" s="4">
-        <v>50.67114093959763</v>
+        <v>57.63795674869591</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2566,25 +3026,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1870887690364498</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03855100925781585</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2744949651841381</v>
+        <v>0.2868722306837412</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2344199879224771</v>
+        <v>0.1280372106060952</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1830268242233686</v>
+        <v>0.2072492138101666</v>
       </c>
       <c r="E4" s="4">
-        <v>51.95918367346939</v>
+        <v>51.79591836734694</v>
       </c>
       <c r="F4" s="4">
-        <v>47.48322147651007</v>
+        <v>51.54362416107382</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -2607,34 +3083,50 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2868722306837412</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1280372106060952</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3430632606014647</v>
+        <v>0.3646908956296329</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>0.05433411764525431</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2344869788332012</v>
+        <v>0.2119225615231926</v>
       </c>
       <c r="E5" s="4">
-        <v>48.5578231292517</v>
+        <v>52.87755102040816</v>
       </c>
       <c r="F5" s="4">
-        <v>29.95973154362419</v>
+        <v>56.85011185682262</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -2648,9 +3140,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3646908956296329</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05433411764525431</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3169,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3177,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3188,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3230,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,75 +3261,107 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8083004838378738</v>
+        <v>0.5957789151007257</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7038746509646897</v>
+        <v>0.3483723393899627</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7222023319355065</v>
+        <v>0.4802161781124307</v>
       </c>
       <c r="E3" s="4">
-        <v>45.14739229024974</v>
+        <v>48.88888888888903</v>
       </c>
       <c r="F3" s="4">
-        <v>41.34041759880711</v>
+        <v>45.24422073079798</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>3</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5957789151007257</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3483723393899627</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4025804029818518</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6185793714464856</v>
-      </c>
+        <v>0.3963628785540602</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.5458469114429183</v>
+        <v>0.3320856596454412</v>
       </c>
       <c r="E4" s="4">
-        <v>39.89795918367347</v>
+        <v>39.60544217687075</v>
       </c>
       <c r="F4" s="4">
-        <v>34.165548098434</v>
+        <v>23.91498881431764</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -2820,34 +3375,48 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3963628785540602</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4349733716688643</v>
+        <v>0.3498992251270979</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5136708437395896</v>
+        <v>0.4444946037472439</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4843611465622013</v>
+        <v>0.4178002746766252</v>
       </c>
       <c r="E5" s="4">
-        <v>38.12925170068028</v>
+        <v>42.30612244897959</v>
       </c>
       <c r="F5" s="4">
-        <v>27.98881431767341</v>
+        <v>37.31767337807607</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -2861,9 +3430,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3498992251270979</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4444946037472439</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3459,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3467,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3478,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3520,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,35 +3551,53 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4483880073167382</v>
+        <v>0.6940909066645856</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1940435244420513</v>
+        <v>0.4945518382565552</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1350628041582015</v>
+        <v>0.3310876924641815</v>
       </c>
       <c r="E3" s="4">
-        <v>55.41383219954675</v>
+        <v>57.73809523809553</v>
       </c>
       <c r="F3" s="4">
-        <v>43.71178225205173</v>
+        <v>50.67114093959763</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
         <v>1</v>
       </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
       <c r="J3" s="5">
         <v>3</v>
       </c>
@@ -2992,34 +3610,48 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6940909066645856</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4945518382565552</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1690770102623929</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.16716544461792</v>
-      </c>
+        <v>0.3430632606014647</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.1712317921990987</v>
+        <v>0.2344869788332012</v>
       </c>
       <c r="E4" s="4">
-        <v>52.19727891156462</v>
+        <v>48.5578231292517</v>
       </c>
       <c r="F4" s="4">
-        <v>49.22371364653244</v>
+        <v>29.95973154362419</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -3033,25 +3665,39 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3430632606014647</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2123253094305987</v>
+        <v>0.2744949651841381</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1802618466840915</v>
+        <v>0.2344199879224771</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1461442545605614</v>
+        <v>0.1830268242233686</v>
       </c>
       <c r="E5" s="4">
-        <v>50.72108843537415</v>
+        <v>51.95918367346939</v>
       </c>
       <c r="F5" s="4">
-        <v>47.05145413870245</v>
+        <v>47.48322147651007</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -3074,9 +3720,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2744949651841381</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2344199879224771</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3749,1458 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.8083004838378738</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7038746509646897</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7222023319355065</v>
+      </c>
+      <c r="E3" s="4">
+        <v>45.14739229024974</v>
+      </c>
+      <c r="F3" s="4">
+        <v>41.34041759880711</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8083004838378738</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7038746509646897</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4349733716688643</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5136708437395896</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4843611465622013</v>
+      </c>
+      <c r="E4" s="4">
+        <v>38.12925170068028</v>
+      </c>
+      <c r="F4" s="4">
+        <v>27.98881431767341</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4349733716688643</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5136708437395896</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4025804029818518</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6185793714464856</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5458469114429183</v>
+      </c>
+      <c r="E5" s="4">
+        <v>39.89795918367347</v>
+      </c>
+      <c r="F5" s="4">
+        <v>34.165548098434</v>
+      </c>
+      <c r="G5" s="5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4025804029818518</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6185793714464856</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4483880073167382</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1940435244420513</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1350628041582015</v>
+      </c>
+      <c r="E3" s="4">
+        <v>55.41383219954675</v>
+      </c>
+      <c r="F3" s="4">
+        <v>43.71178225205173</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4483880073167382</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1940435244420513</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2123253094305987</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1802618466840915</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1461442545605614</v>
+      </c>
+      <c r="E4" s="4">
+        <v>50.72108843537415</v>
+      </c>
+      <c r="F4" s="4">
+        <v>47.05145413870245</v>
+      </c>
+      <c r="G4" s="5">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2123253094305987</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1802618466840915</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1690770102623929</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.16716544461792</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1712317921990987</v>
+      </c>
+      <c r="E5" s="4">
+        <v>52.19727891156462</v>
+      </c>
+      <c r="F5" s="4">
+        <v>49.22371364653244</v>
+      </c>
+      <c r="G5" s="5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1690770102623929</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.16716544461792</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4216212409083546</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3808383877578357</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.573007157300534</v>
+      </c>
+      <c r="K3" s="4">
+        <v>50.68239795918367</v>
+      </c>
+      <c r="L3" s="4">
+        <v>47.30914429530201</v>
+      </c>
+      <c r="M3" s="5">
+        <v>16</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2480989.89033699</v>
+      </c>
+      <c r="O3" s="4">
+        <v>387.957762367004</v>
+      </c>
+      <c r="P3" s="5">
+        <v>6395</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>68.75</v>
+      </c>
+      <c r="E4" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="F4" s="3">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.620078039903117</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3521507170655696</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.758666342352452</v>
+      </c>
+      <c r="K4" s="4">
+        <v>53.20790816326536</v>
+      </c>
+      <c r="L4" s="4">
+        <v>48.87374161073824</v>
+      </c>
+      <c r="M4" s="5">
+        <v>16</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1425890.09976387</v>
+      </c>
+      <c r="O4" s="4">
+        <v>208.0983800005648</v>
+      </c>
+      <c r="P4" s="5">
+        <v>6852</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.3235996541214483</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.06806957261033138</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2414852711806397</v>
+      </c>
+      <c r="K5" s="4">
+        <v>51.61777210884352</v>
+      </c>
+      <c r="L5" s="4">
+        <v>48.91848434004475</v>
+      </c>
+      <c r="M5" s="5">
+        <v>16</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1210530.505418777</v>
+      </c>
+      <c r="O5" s="4">
+        <v>191.1162780894818</v>
+      </c>
+      <c r="P5" s="5">
+        <v>6334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3206441874628077</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1423606033304831</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.4700392542825362</v>
+      </c>
+      <c r="K6" s="4">
+        <v>51.22874149659864</v>
+      </c>
+      <c r="L6" s="4">
+        <v>44.67980984340044</v>
+      </c>
+      <c r="M6" s="5">
+        <v>16</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1065435.245037079</v>
+      </c>
+      <c r="O6" s="4">
+        <v>141.360653447934</v>
+      </c>
+      <c r="P6" s="5">
+        <v>7537</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1975189578429486</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.03944534454428587</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1528656508232906</v>
+      </c>
+      <c r="K7" s="4">
+        <v>53.05059523809524</v>
+      </c>
+      <c r="L7" s="4">
+        <v>48.44519015659955</v>
+      </c>
+      <c r="M7" s="5">
+        <v>16</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1604838.933229446</v>
+      </c>
+      <c r="O7" s="4">
+        <v>236.8066892768845</v>
+      </c>
+      <c r="P7" s="5">
+        <v>6777</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.4183569747664837</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2226520852642399</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.3916152746808239</v>
+      </c>
+      <c r="K8" s="4">
+        <v>51.88137755102041</v>
+      </c>
+      <c r="L8" s="4">
+        <v>45.98154362416108</v>
+      </c>
+      <c r="M8" s="5">
+        <v>16</v>
+      </c>
+      <c r="N8" s="5">
+        <v>537725.3928184509</v>
+      </c>
+      <c r="O8" s="4">
+        <v>86.33997957907049</v>
+      </c>
+      <c r="P8" s="5">
+        <v>6228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C9" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.7722232424879856</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.8593412195821107</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.8669895587907455</v>
+      </c>
+      <c r="K9" s="4">
+        <v>53.45025510204081</v>
+      </c>
+      <c r="L9" s="4">
+        <v>52.08892617449687</v>
+      </c>
+      <c r="M9" s="5">
+        <v>16</v>
+      </c>
+      <c r="N9" s="5">
+        <v>468629.5921802521</v>
+      </c>
+      <c r="O9" s="4">
+        <v>94.6535229610689</v>
+      </c>
+      <c r="P9" s="5">
+        <v>4951</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1744743877134795</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.05930680847951653</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1717806252674854</v>
+      </c>
+      <c r="K10" s="4">
+        <v>54.87244897959184</v>
+      </c>
+      <c r="L10" s="4">
+        <v>46.10598434004476</v>
+      </c>
+      <c r="M10" s="5">
+        <v>16</v>
+      </c>
+      <c r="N10" s="5">
+        <v>581954.4486999512</v>
+      </c>
+      <c r="O10" s="4">
+        <v>87.8024213488158</v>
+      </c>
+      <c r="P10" s="5">
+        <v>6628</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C11" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2842294345991512</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3278787091552715</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.3712487140431939</v>
+      </c>
+      <c r="K11" s="4">
+        <v>53.63945578231292</v>
+      </c>
+      <c r="L11" s="4">
+        <v>45.86968680089486</v>
+      </c>
+      <c r="M11" s="5">
+        <v>16</v>
+      </c>
+      <c r="N11" s="5">
+        <v>663006.9465637207</v>
+      </c>
+      <c r="O11" s="4">
+        <v>96.73284892963535</v>
+      </c>
+      <c r="P11" s="5">
+        <v>6854</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="F12" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2787679902919002</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.07442677884379886</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1950950323707552</v>
+      </c>
+      <c r="K12" s="4">
+        <v>52.98256802721088</v>
+      </c>
+      <c r="L12" s="4">
+        <v>47.59437919463083</v>
+      </c>
+      <c r="M12" s="5">
+        <v>16</v>
+      </c>
+      <c r="N12" s="5">
+        <v>472845.6017971039</v>
+      </c>
+      <c r="O12" s="4">
+        <v>78.67647284477603</v>
+      </c>
+      <c r="P12" s="5">
+        <v>6010</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C13" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D13" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2737717653615981</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.07364077916972178</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2111591545373166</v>
+      </c>
+      <c r="K13" s="4">
+        <v>54.55994897959184</v>
+      </c>
+      <c r="L13" s="4">
+        <v>55.48727628635406</v>
+      </c>
+      <c r="M13" s="5">
+        <v>16</v>
+      </c>
+      <c r="N13" s="5">
+        <v>630316.8060779572</v>
+      </c>
+      <c r="O13" s="4">
+        <v>137.9249028616974</v>
+      </c>
+      <c r="P13" s="5">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>25</v>
+      </c>
+      <c r="C14" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="D14" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.456624000563134</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3964334715686033</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.4144204212678073</v>
+      </c>
+      <c r="K14" s="4">
+        <v>43.93069727891157</v>
+      </c>
+      <c r="L14" s="4">
+        <v>36.10178970917227</v>
+      </c>
+      <c r="M14" s="5">
+        <v>16</v>
+      </c>
+      <c r="N14" s="5">
+        <v>2044435.6944561</v>
+      </c>
+      <c r="O14" s="4">
+        <v>294.502404848185</v>
+      </c>
+      <c r="P14" s="5">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="D15" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.4532710355572205</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.3644859130895162</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2546309481292461</v>
+      </c>
+      <c r="K15" s="4">
+        <v>53.06335034013605</v>
+      </c>
+      <c r="L15" s="4">
+        <v>43.2026006711409</v>
+      </c>
+      <c r="M15" s="5">
+        <v>16</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2151287.494659424</v>
+      </c>
+      <c r="O15" s="4">
+        <v>282.136064873367</v>
+      </c>
+      <c r="P15" s="5">
+        <v>7625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D16" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>50</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5648482360175514</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.6437422565877716</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.5927658926024149</v>
+      </c>
+      <c r="K16" s="4">
+        <v>41.31377551020408</v>
+      </c>
+      <c r="L16" s="4">
+        <v>34.92589485458617</v>
+      </c>
+      <c r="M16" s="5">
+        <v>16</v>
+      </c>
+      <c r="N16" s="5">
+        <v>972489.9475574493</v>
+      </c>
+      <c r="O16" s="4">
+        <v>133.4920998706176</v>
+      </c>
+      <c r="P16" s="5">
+        <v>7285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>31.25</v>
+      </c>
+      <c r="C17" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2873337276478367</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1777796214092149</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1498285661717194</v>
+      </c>
+      <c r="K17" s="4">
+        <v>52.9421768707483</v>
+      </c>
+      <c r="L17" s="4">
+        <v>46.47790827740493</v>
+      </c>
+      <c r="M17" s="5">
+        <v>16</v>
+      </c>
+      <c r="N17" s="5">
+        <v>844284.651517868</v>
+      </c>
+      <c r="O17" s="4">
+        <v>112.9175674091037</v>
+      </c>
+      <c r="P17" s="5">
+        <v>7477</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3253,13 +5361,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3605,13 +5713,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3781,13 +5889,13 @@
         <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +5955,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>8</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>8</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>9</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>6</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>9</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>9</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>7</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>7</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>9</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>9</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>8</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>9</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>9</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>7</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>9</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>6</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>9</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>8</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>7</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>9</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>3</v>
+      </c>
+      <c r="I12" s="5">
+        <v>3</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>5</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>9</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>7</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>4</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>9</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>9</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>9</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>9</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>6</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>6</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>9</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>8</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>8</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>5</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
+        <v>9</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>9</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>6</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6723,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6765,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6796,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5812119249537394</v>
@@ -3960,25 +6855,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5812119249537394</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6310256455039772</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4357875066525821</v>
+        <v>0.2159461543096654</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2472202317657377</v>
+        <v>0.1391756571307212</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5483277517087345</v>
+        <v>0.3099060214002634</v>
       </c>
       <c r="E4" s="4">
-        <v>48.92517006802721</v>
+        <v>47.66666666666666</v>
       </c>
       <c r="F4" s="4">
-        <v>47.5413870246085</v>
+        <v>44.00671140939598</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -4001,25 +6912,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2159461543096654</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1391756571307212</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2159461543096654</v>
+        <v>0.4357875066525821</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1391756571307212</v>
+        <v>0.2472202317657377</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3099060214002634</v>
+        <v>0.5483277517087345</v>
       </c>
       <c r="E5" s="4">
-        <v>47.66666666666666</v>
+        <v>48.92517006802721</v>
       </c>
       <c r="F5" s="4">
-        <v>44.00671140939598</v>
+        <v>47.5413870246085</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -4042,9 +6969,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4357875066525821</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2472202317657377</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +6998,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7017,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7059,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,17 +7090,33 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>3.562430487190776</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
         <v>3.793381796394878</v>
       </c>
@@ -4173,25 +7147,39 @@
       <c r="M3" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>3.562430487190776</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5306521611935977</v>
+        <v>0.3786809818674442</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3417982594909574</v>
+        <v>0.3625031746401817</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6357835965878849</v>
+        <v>0.4398905432661081</v>
       </c>
       <c r="E4" s="4">
-        <v>53.04761904761904</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="F4" s="4">
-        <v>50.3937360178971</v>
+        <v>46.39149888143177</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -4214,25 +7202,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3786809818674442</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3625031746401817</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3786809818674442</v>
+        <v>0.5306521611935977</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3625031746401817</v>
+        <v>0.3417982594909574</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4398905432661081</v>
+        <v>0.6357835965878849</v>
       </c>
       <c r="E5" s="4">
-        <v>51.66666666666666</v>
+        <v>53.04761904761904</v>
       </c>
       <c r="F5" s="4">
-        <v>46.39149888143177</v>
+        <v>50.3937360178971</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -4255,9 +7259,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5306521611935977</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3417982594909574</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7288,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7307,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7349,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7380,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4648354155547547</v>
@@ -4386,25 +7439,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4648354155547547</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03951553907015182</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2645854635172327</v>
+        <v>0.2131309310056963</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1501888347921465</v>
+        <v>0.01450434396869582</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2602334030790416</v>
+        <v>0.2305217403324491</v>
       </c>
       <c r="E4" s="4">
-        <v>49.31972789115648</v>
+        <v>49.02040816326531</v>
       </c>
       <c r="F4" s="4">
-        <v>46.38702460850072</v>
+        <v>47.3758389261745</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -4427,25 +7496,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2131309310056963</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.01450434396869582</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2131309310056963</v>
+        <v>0.2645854635172327</v>
       </c>
       <c r="C5" s="4">
-        <v>0.01450434396869582</v>
+        <v>0.1501888347921465</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2305217403324491</v>
+        <v>0.2602334030790416</v>
       </c>
       <c r="E5" s="4">
-        <v>49.02040816326531</v>
+        <v>49.31972789115648</v>
       </c>
       <c r="F5" s="4">
-        <v>47.3758389261745</v>
+        <v>46.38702460850072</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -4468,9 +7553,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2645854635172327</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1501888347921465</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7582,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7601,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7643,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7674,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4053213585402394</v>
@@ -4599,25 +7733,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4053213585402394</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3292808822613722</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.304317017150629</v>
+        <v>0.2353587524820682</v>
       </c>
       <c r="C4" s="4">
-        <v>0.0488857762756254</v>
+        <v>0.04891515145445169</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4675207334287051</v>
+        <v>0.3244270956953074</v>
       </c>
       <c r="E4" s="4">
-        <v>48.22448979591837</v>
+        <v>50.24489795918367</v>
       </c>
       <c r="F4" s="4">
-        <v>41.7248322147651</v>
+        <v>45.99328859060402</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -4640,25 +7790,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2353587524820682</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04891515145445169</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2353587524820682</v>
+        <v>0.304317017150629</v>
       </c>
       <c r="C5" s="4">
-        <v>0.04891515145445169</v>
+        <v>0.0488857762756254</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3244270956953074</v>
+        <v>0.4675207334287051</v>
       </c>
       <c r="E5" s="4">
-        <v>50.24489795918367</v>
+        <v>48.22448979591837</v>
       </c>
       <c r="F5" s="4">
-        <v>45.99328859060402</v>
+        <v>41.7248322147651</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -4681,9 +7847,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.304317017150629</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0488857762756254</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7876,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7895,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +7937,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +7968,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2398675271854624</v>
@@ -4812,25 +8027,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2398675271854624</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04700019874391614</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1198399154477556</v>
+        <v>0.224379717027125</v>
       </c>
       <c r="C4" s="4">
-        <v>0.03238777947998983</v>
+        <v>0.03894805540895163</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1163584464116184</v>
+        <v>0.1147085205270855</v>
       </c>
       <c r="E4" s="4">
-        <v>51.36734693877551</v>
+        <v>49.95918367346939</v>
       </c>
       <c r="F4" s="4">
-        <v>48.00671140939598</v>
+        <v>45.74496644295302</v>
       </c>
       <c r="G4" s="5">
         <v>5</v>
@@ -4853,25 +8084,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.224379717027125</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03894805540895163</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.224379717027125</v>
+        <v>0.1198399154477556</v>
       </c>
       <c r="C5" s="4">
-        <v>0.03894805540895163</v>
+        <v>0.03238777947998983</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1147085205270855</v>
+        <v>0.1163584464116184</v>
       </c>
       <c r="E5" s="4">
-        <v>49.95918367346939</v>
+        <v>51.36734693877551</v>
       </c>
       <c r="F5" s="4">
-        <v>45.74496644295302</v>
+        <v>48.00671140939598</v>
       </c>
       <c r="G5" s="5">
         <v>5</v>
@@ -4894,9 +8141,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1198399154477556</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03238777947998983</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8170,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5442778698846867</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4560612804782605</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5353602268401397</v>
-      </c>
-      <c r="E3" s="4">
-        <v>56.19047619047646</v>
-      </c>
-      <c r="F3" s="4">
-        <v>49.98322147651101</v>
-      </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>3</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3823283592277328</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.03695920820657239</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3303512530008025</v>
-      </c>
-      <c r="E4" s="4">
-        <v>49.81632653061224</v>
-      </c>
-      <c r="F4" s="4">
-        <v>44.74496644295302</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.303280516163391</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.05823116950087659</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2803853537696664</v>
-      </c>
-      <c r="E5" s="4">
-        <v>48.77551020408163</v>
-      </c>
-      <c r="F5" s="4">
-        <v>42.41610738255034</v>
-      </c>
-      <c r="G5" s="5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.8452845343086892</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.9126482299786574</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.992285515979025</v>
-      </c>
-      <c r="E3" s="4">
-        <v>57.65306122449013</v>
-      </c>
-      <c r="F3" s="4">
-        <v>54.6718866517523</v>
-      </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.8941001134641056</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.033865405792227</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.9432829099423771</v>
-      </c>
-      <c r="E4" s="4">
-        <v>50.83673469387755</v>
-      </c>
-      <c r="F4" s="4">
-        <v>50.77628635346756</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>3</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.5626728213270212</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.6315100229754478</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6403410590131784</v>
-      </c>
-      <c r="E5" s="4">
-        <v>51.02040816326531</v>
-      </c>
-      <c r="F5" s="4">
-        <v>50.30201342281873</v>
-      </c>
-      <c r="G5" s="5">
-        <v>5</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
